--- a/data/trans_orig/P33A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373504</t>
+          <t>374651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>404282</t>
+          <t>404003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>309884</t>
+          <t>311149</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>347345</t>
+          <t>348599</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>699215</t>
+          <t>695036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>743657</t>
+          <t>742041</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46897</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77675</t>
+          <t>76528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81922</t>
+          <t>80668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119383</t>
+          <t>118118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136789</t>
+          <t>138405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181231</t>
+          <t>185410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>553951</t>
+          <t>554255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>593350</t>
+          <t>589965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>437426</t>
+          <t>433773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>479168</t>
+          <t>481058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1005027</t>
+          <t>1003815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1060103</t>
+          <t>1061846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>95248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131262</t>
+          <t>130958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130023</t>
+          <t>128133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171765</t>
+          <t>175418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234301</t>
+          <t>232558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>289377</t>
+          <t>290589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>536827</t>
+          <t>538067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>577256</t>
+          <t>575501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>491265</t>
+          <t>488336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>538244</t>
+          <t>536546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1041455</t>
+          <t>1041060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1103308</t>
+          <t>1104737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94964</t>
+          <t>96719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>134153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162966</t>
+          <t>164664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>209945</t>
+          <t>212874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270122</t>
+          <t>268693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331975</t>
+          <t>332370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>500030</t>
+          <t>501094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>539120</t>
+          <t>538750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>400319</t>
+          <t>399021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449486</t>
+          <t>450058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>916507</t>
+          <t>914372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>978967</t>
+          <t>976703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,85%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71007</t>
+          <t>71377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110097</t>
+          <t>109033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163527</t>
+          <t>162955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212694</t>
+          <t>213992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>244173</t>
+          <t>246437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306633</t>
+          <t>308768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>332828</t>
+          <t>333567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>366578</t>
+          <t>366398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275697</t>
+          <t>276324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316758</t>
+          <t>314401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>621122</t>
+          <t>619369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>674771</t>
+          <t>671885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61810</t>
+          <t>61990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95560</t>
+          <t>94821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125890</t>
+          <t>128247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166951</t>
+          <t>166324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196265</t>
+          <t>199151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249914</t>
+          <t>251667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>259549</t>
+          <t>260696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>282802</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251096</t>
+          <t>250935</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282149</t>
+          <t>282721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>519067</t>
+          <t>517648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>560789</t>
+          <t>559088</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50237</t>
+          <t>49090</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69855</t>
+          <t>69283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100908</t>
+          <t>101069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101002</t>
+          <t>102703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142724</t>
+          <t>144143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202678</t>
+          <t>205587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>227231</t>
+          <t>226835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>278677</t>
+          <t>278558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>312418</t>
+          <t>314055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>491672</t>
+          <t>492670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>535038</t>
+          <t>533021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42047</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>70386</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105764</t>
+          <t>105883</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94128</t>
+          <t>96145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>137494</t>
+          <t>136496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2846952</t>
+          <t>2845639</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2930374</t>
+          <t>2929184</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2533864</t>
+          <t>2541286</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2643192</t>
+          <t>2650275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5407116</t>
+          <t>5409254</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5548949</t>
+          <t>5550043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471264</t>
+          <t>472454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>554686</t>
+          <t>555999</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>888582</t>
+          <t>881499</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>997910</t>
+          <t>990488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1384463</t>
+          <t>1383369</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1526296</t>
+          <t>1524158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>339300</t>
+          <t>341778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>370114</t>
+          <t>371795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291372</t>
+          <t>291883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>322231</t>
+          <t>322802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>642154</t>
+          <t>643004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>686010</t>
+          <t>686875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>44637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77132</t>
+          <t>74654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70680</t>
+          <t>70109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101539</t>
+          <t>101028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123333</t>
+          <t>122468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167189</t>
+          <t>166339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>460558</t>
+          <t>459205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>499614</t>
+          <t>497159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>411375</t>
+          <t>409306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>449361</t>
+          <t>448747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>884190</t>
+          <t>881224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>939346</t>
+          <t>936776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81361</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120417</t>
+          <t>121770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109898</t>
+          <t>110512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147884</t>
+          <t>149953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200888</t>
+          <t>203458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256044</t>
+          <t>259010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>522830</t>
+          <t>522819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>563737</t>
+          <t>562760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>466643</t>
+          <t>468414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>510262</t>
+          <t>513095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1001567</t>
+          <t>1005968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1064116</t>
+          <t>1065097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97777</t>
+          <t>98754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138684</t>
+          <t>138695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143064</t>
+          <t>140231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186683</t>
+          <t>184912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250724</t>
+          <t>249743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313273</t>
+          <t>308872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>509752</t>
+          <t>507466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548416</t>
+          <t>547376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>420836</t>
+          <t>420727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>467711</t>
+          <t>467505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>941252</t>
+          <t>941655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1004054</t>
+          <t>1005620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>93381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131005</t>
+          <t>133291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173664</t>
+          <t>173870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220539</t>
+          <t>220648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278078</t>
+          <t>276512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340880</t>
+          <t>340477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>387739</t>
+          <t>388722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>419650</t>
+          <t>420306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319319</t>
+          <t>322460</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364023</t>
+          <t>365545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>720286</t>
+          <t>720209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>772208</t>
+          <t>774288</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53227</t>
+          <t>52571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85138</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126314</t>
+          <t>124792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171018</t>
+          <t>167877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191006</t>
+          <t>188926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>271595</t>
+          <t>273390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>296271</t>
+          <t>297338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251301</t>
+          <t>250645</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>285721</t>
+          <t>285775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>530157</t>
+          <t>531848</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>573748</t>
+          <t>574548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>32554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58297</t>
+          <t>56502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85072</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119492</t>
+          <t>120148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126938</t>
+          <t>126138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170529</t>
+          <t>168838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>216222</t>
+          <t>216176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234394</t>
+          <t>234145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>273806</t>
+          <t>271276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>309355</t>
+          <t>309822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>495161</t>
+          <t>493598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>538756</t>
+          <t>538606</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20925</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39097</t>
+          <t>39143</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80597</t>
+          <t>80130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116146</t>
+          <t>118676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>106515</t>
+          <t>106665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>150110</t>
+          <t>151673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2780307</t>
+          <t>2781398</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2867078</t>
+          <t>2867936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2518655</t>
+          <t>2525687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2629061</t>
+          <t>2631907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5332697</t>
+          <t>5337494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5473929</t>
+          <t>5476983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,89%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>490686</t>
+          <t>489828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>577457</t>
+          <t>576366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>868894</t>
+          <t>866048</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>979300</t>
+          <t>972268</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1381790</t>
+          <t>1378736</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1523022</t>
+          <t>1518225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>350075</t>
+          <t>351552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>383150</t>
+          <t>383717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254411</t>
+          <t>256068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286206</t>
+          <t>286089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617745</t>
+          <t>620864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>665273</t>
+          <t>664916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46089</t>
+          <t>44612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>53182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87669</t>
+          <t>84550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>347585</t>
+          <t>350077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384036</t>
+          <t>385609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>409713</t>
+          <t>411678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>459726</t>
+          <t>461871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>774799</t>
+          <t>775451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>832321</t>
+          <t>835799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75962</t>
+          <t>73470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46145</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96158</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97097</t>
+          <t>93619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154619</t>
+          <t>153967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415370</t>
+          <t>417360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>455815</t>
+          <t>452319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,17 +7406,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>416463</t>
+          <t>416462</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>399510</t>
+          <t>400752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>432973</t>
+          <t>433706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>826617</t>
+          <t>826715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>874733</t>
+          <t>877910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77382</t>
+          <t>80878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117827</t>
+          <t>115837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,17 +7519,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120303</t>
+          <t>120304</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103793</t>
+          <t>103060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137256</t>
+          <t>136014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195230</t>
+          <t>192053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243346</t>
+          <t>243248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>695284</t>
+          <t>693958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>826078</t>
+          <t>828482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510210</t>
+          <t>509469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>559172</t>
+          <t>559923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1221154</t>
+          <t>1222549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1416797</t>
+          <t>1416287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60648</t>
+          <t>58244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191442</t>
+          <t>192768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150448</t>
+          <t>149697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>199410</t>
+          <t>200151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179550</t>
+          <t>180060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375193</t>
+          <t>373798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>424553</t>
+          <t>422712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>459775</t>
+          <t>458344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>335073</t>
+          <t>333533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366237</t>
+          <t>366056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>767423</t>
+          <t>767662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>819291</t>
+          <t>818975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96166</t>
+          <t>97597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131388</t>
+          <t>133229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175524</t>
+          <t>175705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206688</t>
+          <t>208228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278410</t>
+          <t>278726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330278</t>
+          <t>330039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>285856</t>
+          <t>285571</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>309254</t>
+          <t>309349</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>424188</t>
+          <t>423760</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>557811</t>
+          <t>561001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>731263</t>
+          <t>732148</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>872701</t>
+          <t>878806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56547</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79945</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49971</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183594</t>
+          <t>184022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100882</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242320</t>
+          <t>241435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189349</t>
+          <t>193045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214256</t>
+          <t>215602</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>268049</t>
+          <t>267706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295275</t>
+          <t>295683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>465784</t>
+          <t>469469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>503183</t>
+          <t>504609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92714</t>
+          <t>89018</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127701</t>
+          <t>127293</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>155270</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201856</t>
+          <t>200430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239255</t>
+          <t>235570</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2815441</t>
+          <t>2817174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3019981</t>
+          <t>3008245</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2701516</t>
+          <t>2698962</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2958545</t>
+          <t>2930686</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5531279</t>
+          <t>5548185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5816066</t>
+          <t>5831254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>423458</t>
+          <t>435194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>627998</t>
+          <t>626265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675481</t>
+          <t>703340</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>932510</t>
+          <t>935064</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1261399</t>
+          <t>1246211</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1546186</t>
+          <t>1529280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>374651</t>
+          <t>374701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>404003</t>
+          <t>403764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>311149</t>
+          <t>312293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>348599</t>
+          <t>347571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>695036</t>
+          <t>695957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>742041</t>
+          <t>743382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>47415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>76478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80668</t>
+          <t>81696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118118</t>
+          <t>116974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138405</t>
+          <t>137064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185410</t>
+          <t>184489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>554255</t>
+          <t>554441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>589965</t>
+          <t>593006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>433773</t>
+          <t>435828</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>481058</t>
+          <t>479193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1003815</t>
+          <t>1004555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1061846</t>
+          <t>1064418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95248</t>
+          <t>92207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130958</t>
+          <t>130772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128133</t>
+          <t>129998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175418</t>
+          <t>173363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232558</t>
+          <t>229986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290589</t>
+          <t>289849</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>538067</t>
+          <t>537843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>575501</t>
+          <t>576988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>488336</t>
+          <t>489729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>536546</t>
+          <t>538355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1041060</t>
+          <t>1041273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1104737</t>
+          <t>1101536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96719</t>
+          <t>95232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134153</t>
+          <t>134377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164664</t>
+          <t>162855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>212874</t>
+          <t>211481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268693</t>
+          <t>271894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>332157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>501094</t>
+          <t>501182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>538750</t>
+          <t>538783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399021</t>
+          <t>401462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>450058</t>
+          <t>450419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>914372</t>
+          <t>915504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>976703</t>
+          <t>976626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71377</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109033</t>
+          <t>108945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162955</t>
+          <t>162594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213992</t>
+          <t>211551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246437</t>
+          <t>246514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308768</t>
+          <t>307636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>335448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>366398</t>
+          <t>366864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>276324</t>
+          <t>272354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>314401</t>
+          <t>314685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>619369</t>
+          <t>619607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>671885</t>
+          <t>674285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61990</t>
+          <t>61524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94821</t>
+          <t>92940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128247</t>
+          <t>127963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166324</t>
+          <t>170294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>199151</t>
+          <t>196751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251667</t>
+          <t>251429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>260696</t>
+          <t>259952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>285056</t>
+          <t>283876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250935</t>
+          <t>251344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282721</t>
+          <t>284280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>517648</t>
+          <t>520112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>559088</t>
+          <t>559415</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49090</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69283</t>
+          <t>67724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101069</t>
+          <t>100660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102703</t>
+          <t>102376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144143</t>
+          <t>141679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205587</t>
+          <t>205199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>226835</t>
+          <t>227209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>278558</t>
+          <t>279714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314055</t>
+          <t>313862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>492670</t>
+          <t>494409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>533021</t>
+          <t>535717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39138</t>
+          <t>39526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70386</t>
+          <t>70579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105883</t>
+          <t>104727</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96145</t>
+          <t>93449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>136496</t>
+          <t>134757</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2845639</t>
+          <t>2839887</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2929184</t>
+          <t>2926110</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2541286</t>
+          <t>2535855</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2650275</t>
+          <t>2647044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5409254</t>
+          <t>5410910</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5550043</t>
+          <t>5545467</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>472454</t>
+          <t>475528</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>555999</t>
+          <t>561751</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>881499</t>
+          <t>884730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>990488</t>
+          <t>995919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1383369</t>
+          <t>1387945</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1524158</t>
+          <t>1522502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>341778</t>
+          <t>341823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>371795</t>
+          <t>371141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291883</t>
+          <t>292751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>322802</t>
+          <t>323527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>643004</t>
+          <t>639881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>686875</t>
+          <t>685310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>45291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>74609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70109</t>
+          <t>69384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101028</t>
+          <t>100160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122468</t>
+          <t>124033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166339</t>
+          <t>169462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>459205</t>
+          <t>461476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>497159</t>
+          <t>498861</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>409306</t>
+          <t>409838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>881224</t>
+          <t>882962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>936776</t>
+          <t>934048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83816</t>
+          <t>82114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121770</t>
+          <t>119499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149953</t>
+          <t>149421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203458</t>
+          <t>206186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259010</t>
+          <t>257272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>522819</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>562760</t>
+          <t>561900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>468414</t>
+          <t>469055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>513095</t>
+          <t>512743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1005968</t>
+          <t>1004092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1065097</t>
+          <t>1064696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98754</t>
+          <t>99614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138695</t>
+          <t>138849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140231</t>
+          <t>140583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184912</t>
+          <t>184271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249743</t>
+          <t>250144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308872</t>
+          <t>310748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>507466</t>
+          <t>507889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547376</t>
+          <t>550193</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>420727</t>
+          <t>422410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>467505</t>
+          <t>468379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>941655</t>
+          <t>939264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1005620</t>
+          <t>1006213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93381</t>
+          <t>90564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133291</t>
+          <t>132868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173870</t>
+          <t>172996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>218965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>275919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340477</t>
+          <t>342868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>388722</t>
+          <t>387833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>420306</t>
+          <t>419758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>322460</t>
+          <t>320489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>365545</t>
+          <t>364276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>720209</t>
+          <t>722754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>774288</t>
+          <t>776462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52571</t>
+          <t>53119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84155</t>
+          <t>85044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124792</t>
+          <t>126061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167877</t>
+          <t>169848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188926</t>
+          <t>186752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243005</t>
+          <t>240460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>273390</t>
+          <t>271060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>297338</t>
+          <t>297033</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250645</t>
+          <t>250385</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>285775</t>
+          <t>284016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>531848</t>
+          <t>530302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>574548</t>
+          <t>574195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56502</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85018</t>
+          <t>86777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120148</t>
+          <t>120408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126138</t>
+          <t>126491</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168838</t>
+          <t>170384</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>216176</t>
+          <t>216472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234145</t>
+          <t>234481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>271276</t>
+          <t>273015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>309822</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493598</t>
+          <t>495482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>538606</t>
+          <t>539497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39143</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>78212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118676</t>
+          <t>116937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>106665</t>
+          <t>105774</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>151673</t>
+          <t>149789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2781398</t>
+          <t>2782116</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2867936</t>
+          <t>2866482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2525687</t>
+          <t>2519415</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2631907</t>
+          <t>2626052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5337494</t>
+          <t>5338511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5476983</t>
+          <t>5475874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>489828</t>
+          <t>491282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>576366</t>
+          <t>575648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>866048</t>
+          <t>871903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>972268</t>
+          <t>978540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1378736</t>
+          <t>1379845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1518225</t>
+          <t>1517208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>371923</t>
+          <t>380827</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351552</t>
+          <t>364706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>383717</t>
+          <t>393156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>273112</t>
+          <t>312811</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256068</t>
+          <t>293159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286089</t>
+          <t>329550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,32 +6755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>645035</t>
+          <t>693638</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>620864</t>
+          <t>666494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>664916</t>
+          <t>713730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -6798,32 +6798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>23576</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36138</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>65444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6868,32 +6868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>69368</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>49276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84550</t>
+          <t>96512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>396164</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>396164</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>396164</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>309250</t>
+          <t>358603</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>309250</t>
+          <t>358603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>309250</t>
+          <t>358603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>705414</t>
+          <t>763006</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>705414</t>
+          <t>763006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>705414</t>
+          <t>763006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,32 +7028,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>369188</t>
+          <t>415949</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>350077</t>
+          <t>394241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>385609</t>
+          <t>432043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>432759</t>
+          <t>415117</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>411678</t>
+          <t>395958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>461871</t>
+          <t>431410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,32 +7098,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>801947</t>
+          <t>831066</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>775451</t>
+          <t>799844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>835799</t>
+          <t>855620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -7141,32 +7141,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73470</t>
+          <t>82649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7176,32 +7176,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>73112</t>
+          <t>80160</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>63867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94193</t>
+          <t>99319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>127471</t>
+          <t>141101</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93619</t>
+          <t>116547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153967</t>
+          <t>172323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505871</t>
+          <t>495277</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505871</t>
+          <t>495277</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505871</t>
+          <t>495277</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>929418</t>
+          <t>972167</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>929418</t>
+          <t>972167</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>929418</t>
+          <t>972167</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,32 +7371,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>436549</t>
+          <t>514966</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>417360</t>
+          <t>493991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>452319</t>
+          <t>534051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>416462</t>
+          <t>473754</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>400752</t>
+          <t>456332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>433706</t>
+          <t>491594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>853011</t>
+          <t>988721</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>826715</t>
+          <t>957901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>877910</t>
+          <t>1014557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -7484,32 +7484,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96648</t>
+          <t>102724</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80878</t>
+          <t>83639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115837</t>
+          <t>123699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120304</t>
+          <t>142459</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103060</t>
+          <t>124619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136014</t>
+          <t>159881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>216952</t>
+          <t>245182</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192053</t>
+          <t>219346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243248</t>
+          <t>276002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533197</t>
+          <t>617690</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533197</t>
+          <t>617690</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533197</t>
+          <t>617690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>536766</t>
+          <t>616213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>536766</t>
+          <t>616213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>536766</t>
+          <t>616213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1069963</t>
+          <t>1233903</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1069963</t>
+          <t>1233903</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1069963</t>
+          <t>1233903</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>757556</t>
+          <t>568638</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>693958</t>
+          <t>546245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>828482</t>
+          <t>588295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>530725</t>
+          <t>537258</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>509469</t>
+          <t>517200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>559923</t>
+          <t>556523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1288281</t>
+          <t>1105896</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1222549</t>
+          <t>1077680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1416287</t>
+          <t>1134147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>129170</t>
+          <t>130847</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58244</t>
+          <t>111190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192768</t>
+          <t>153240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>178895</t>
+          <t>196193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149697</t>
+          <t>176928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200151</t>
+          <t>216251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>308066</t>
+          <t>327040</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180060</t>
+          <t>298789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>373798</t>
+          <t>355256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886726</t>
+          <t>699485</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886726</t>
+          <t>699485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886726</t>
+          <t>699485</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709620</t>
+          <t>733451</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709620</t>
+          <t>733451</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709620</t>
+          <t>733451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1596347</t>
+          <t>1432936</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1596347</t>
+          <t>1432936</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1596347</t>
+          <t>1432936</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>442292</t>
+          <t>483544</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>422712</t>
+          <t>465531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>458344</t>
+          <t>500542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>349874</t>
+          <t>388678</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>333533</t>
+          <t>369657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>366056</t>
+          <t>405527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>792165</t>
+          <t>872222</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>767662</t>
+          <t>843735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>818975</t>
+          <t>897115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>113649</t>
+          <t>120279</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97597</t>
+          <t>103281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133229</t>
+          <t>138292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>191887</t>
+          <t>215468</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175705</t>
+          <t>198619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208228</t>
+          <t>234489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>305536</t>
+          <t>335747</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278726</t>
+          <t>310854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330039</t>
+          <t>364234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>555941</t>
+          <t>603823</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>555941</t>
+          <t>603823</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>555941</t>
+          <t>603823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541761</t>
+          <t>604146</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541761</t>
+          <t>604146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541761</t>
+          <t>604146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1097701</t>
+          <t>1207969</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1097701</t>
+          <t>1207969</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1097701</t>
+          <t>1207969</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>297996</t>
+          <t>328777</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>285571</t>
+          <t>315042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>309349</t>
+          <t>340952</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>490014</t>
+          <t>308273</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>423760</t>
+          <t>294147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>561001</t>
+          <t>322856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>788010</t>
+          <t>637050</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>732148</t>
+          <t>617961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>878806</t>
+          <t>657500</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67805</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56452</t>
+          <t>63268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80230</t>
+          <t>89178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>117768</t>
+          <t>130225</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46781</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184022</t>
+          <t>144351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>185573</t>
+          <t>205668</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94777</t>
+          <t>185218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241435</t>
+          <t>224757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365801</t>
+          <t>404220</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365801</t>
+          <t>404220</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365801</t>
+          <t>404220</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607782</t>
+          <t>438498</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607782</t>
+          <t>438498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607782</t>
+          <t>438498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973583</t>
+          <t>842718</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973583</t>
+          <t>842718</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973583</t>
+          <t>842718</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>203677</t>
+          <t>222588</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193045</t>
+          <t>208552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215602</t>
+          <t>235413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>282757</t>
+          <t>305782</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>267706</t>
+          <t>290735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>295683</t>
+          <t>319901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>486435</t>
+          <t>528371</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>469469</t>
+          <t>507629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>504609</t>
+          <t>548911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>78386</t>
+          <t>86758</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>66461</t>
+          <t>73933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89018</t>
+          <t>100794</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>140219</t>
+          <t>155650</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127293</t>
+          <t>141531</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155270</t>
+          <t>170697</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>218604</t>
+          <t>242407</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>200430</t>
+          <t>221867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>235570</t>
+          <t>263149</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282063</t>
+          <t>309346</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282063</t>
+          <t>309346</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282063</t>
+          <t>309346</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>422976</t>
+          <t>461432</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>422976</t>
+          <t>461432</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>422976</t>
+          <t>461432</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705039</t>
+          <t>770778</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705039</t>
+          <t>770778</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705039</t>
+          <t>770778</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2879182</t>
+          <t>2915291</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2817174</t>
+          <t>2862662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3008245</t>
+          <t>2963252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2775703</t>
+          <t>2741673</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2698962</t>
+          <t>2694831</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2930686</t>
+          <t>2785051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5654885</t>
+          <t>5656964</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5548185</t>
+          <t>5593634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5831254</t>
+          <t>5724172</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>564257</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>435194</t>
+          <t>552606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>626265</t>
+          <t>653196</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>858323</t>
+          <t>965947</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>703340</t>
+          <t>922569</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>935064</t>
+          <t>1012789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1422580</t>
+          <t>1566514</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1246211</t>
+          <t>1499306</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1529280</t>
+          <t>1629844</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3443439</t>
+          <t>3515858</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3634026</t>
+          <t>3707620</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7077465</t>
+          <t>7223478</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
